--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,9 +571,14 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -612,25 +617,25 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>24.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="O2" t="n">
-        <v>182.6666666666667</v>
+        <v>181.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="S2" t="n">
-        <v>4775000</v>
+        <v>5500000</v>
       </c>
       <c r="T2" t="n">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="U2" t="n">
         <v>19.33333333333333</v>
@@ -661,9 +666,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">bank of america stadium
@@ -733,9 +743,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">audi field
@@ -770,46 +785,46 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>28.66666666666667</v>
+        <v>26.25</v>
       </c>
       <c r="O4" t="n">
-        <v>186.6666666666667</v>
+        <v>185.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="S4" t="n">
-        <v>5250000</v>
+        <v>3000000</v>
       </c>
       <c r="T4" t="n">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>25.25</v>
       </c>
       <c r="V4" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>63</v>
+        <v>279</v>
       </c>
       <c r="Z4" t="n">
-        <v>1200000</v>
+        <v>8600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
@@ -819,9 +834,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -864,25 +884,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.83333333333333</v>
+        <v>25.375</v>
       </c>
       <c r="O5" t="n">
-        <v>182.6666666666667</v>
+        <v>180.875</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>1.875</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>413</v>
+        <v>587</v>
       </c>
       <c r="S5" t="n">
-        <v>22925000</v>
+        <v>78425000</v>
       </c>
       <c r="T5" t="n">
-        <v>462</v>
+        <v>636</v>
       </c>
       <c r="U5" t="n">
         <v>37</v>
@@ -913,9 +933,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo field
@@ -954,46 +979,46 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>26.5</v>
+        <v>29.2</v>
       </c>
       <c r="O6" t="n">
-        <v>183</v>
+        <v>181.2</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>128</v>
+        <v>342</v>
       </c>
       <c r="S6" t="n">
-        <v>1300000</v>
+        <v>5775000</v>
       </c>
       <c r="T6" t="n">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="U6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V6" t="n">
-        <v>178.5</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>130</v>
+        <v>392</v>
       </c>
       <c r="Z6" t="n">
-        <v>1650000</v>
+        <v>6050000</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
@@ -1003,9 +1028,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.86458333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -1042,34 +1072,52 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>183</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>138</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>141</v>
+      </c>
       <c r="U7" t="n">
-        <v>26.66666666666667</v>
+        <v>28.8</v>
       </c>
       <c r="V7" t="n">
-        <v>180.3333333333333</v>
+        <v>179</v>
       </c>
       <c r="W7" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>181</v>
+        <v>353</v>
       </c>
       <c r="Z7" t="n">
-        <v>1055000</v>
+        <v>15575000</v>
       </c>
       <c r="AA7" t="n">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
@@ -1079,9 +1127,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">q2 stadium
@@ -1155,9 +1208,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">toyota stadium
@@ -1249,9 +1307,14 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -1288,7 +1351,11 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
       <c r="N10" t="n">
         <v>20</v>
       </c>
@@ -1339,9 +1406,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1433,9 +1505,14 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">citypark
@@ -1506,6 +1583,192 @@
         <v>143</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>30</v>
+      </c>
+      <c r="O13" t="n">
+        <v>175</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>73</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>132</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>141</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>178</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -1099,10 +1099,10 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="V7" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
@@ -1111,13 +1111,13 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Z7" t="n">
-        <v>15575000</v>
+        <v>11175000</v>
       </c>
       <c r="AA7" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>26.5</v>
       </c>
       <c r="O14" t="n">
-        <v>181.5</v>
+        <v>183</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1739,13 +1739,13 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="S14" t="n">
-        <v>2500000</v>
+        <v>6800000</v>
       </c>
       <c r="T14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U14" t="n">
         <v>26</v>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,35 +567,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -612,85 +612,89 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
       <c r="N2" t="n">
-        <v>25.5</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
+        <v>186</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>63</v>
+      </c>
+      <c r="S2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25</v>
+      </c>
+      <c r="V2" t="n">
         <v>181.5</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>258</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>275</v>
-      </c>
-      <c r="U2" t="n">
-        <v>19.33333333333333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>180</v>
-      </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="Z2" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>210</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74500</v>
+        <v>20000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -706,68 +710,81 @@
         <v>2024</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>256</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>277</v>
+      </c>
       <c r="U3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V3" t="n">
-        <v>186.5</v>
+        <v>175</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="Z3" t="n">
-        <v>615000</v>
+        <v>875000</v>
       </c>
       <c r="AA3" t="n">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -782,34 +799,38 @@
       <c r="K4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>26.25</v>
+        <v>26.5</v>
       </c>
       <c r="O4" t="n">
-        <v>185.75</v>
+        <v>183</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="S4" t="n">
-        <v>3000000</v>
+        <v>3625000</v>
       </c>
       <c r="T4" t="n">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>25.25</v>
+        <v>25.5</v>
       </c>
       <c r="V4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -818,47 +839,47 @@
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z4" t="n">
-        <v>8600000</v>
+        <v>11275000</v>
       </c>
       <c r="AA4" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -873,91 +894,87 @@
       <c r="K5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.375</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>180.875</v>
+        <v>180</v>
       </c>
       <c r="P5" t="n">
-        <v>1.875</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>587</v>
+        <v>170</v>
       </c>
       <c r="S5" t="n">
-        <v>78425000</v>
+        <v>1600000</v>
       </c>
       <c r="T5" t="n">
-        <v>636</v>
+        <v>210</v>
       </c>
       <c r="U5" t="n">
-        <v>37</v>
+        <v>29.2</v>
       </c>
       <c r="V5" t="n">
-        <v>186</v>
+        <v>181.2</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>63</v>
+        <v>342</v>
       </c>
       <c r="Z5" t="n">
-        <v>50000</v>
+        <v>5775000</v>
       </c>
       <c r="AA5" t="n">
-        <v>63</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30991</v>
+        <v>25500</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -972,87 +989,87 @@
       <c r="K6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
       <c r="N6" t="n">
-        <v>29.2</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>181.2</v>
+        <v>186.5</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="S6" t="n">
-        <v>5775000</v>
+        <v>615000</v>
       </c>
       <c r="T6" t="n">
-        <v>347</v>
+        <v>143</v>
       </c>
       <c r="U6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V6" t="n">
-        <v>179.3333333333333</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>392</v>
+        <v>201</v>
       </c>
       <c r="Z6" t="n">
-        <v>6050000</v>
+        <v>3275000</v>
       </c>
       <c r="AA6" t="n">
-        <v>411</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26000</v>
+        <v>18500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1069,89 +1086,85 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>vZraQYnO</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>26.5</v>
+        <v>28.8</v>
       </c>
       <c r="O7" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="S7" t="n">
-        <v>3625000</v>
+        <v>15575000</v>
       </c>
       <c r="T7" t="n">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="U7" t="n">
-        <v>28.8</v>
+        <v>34</v>
       </c>
       <c r="V7" t="n">
         <v>179</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>353</v>
+        <v>68</v>
       </c>
       <c r="Z7" t="n">
-        <v>15575000</v>
+        <v>550000</v>
       </c>
       <c r="AA7" t="n">
-        <v>360</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20700</v>
+        <v>19400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1168,71 +1181,89 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O8" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>133</v>
+      </c>
+      <c r="S8" t="n">
+        <v>18700000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>140</v>
+      </c>
       <c r="U8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V8" t="n">
-        <v>183.5</v>
+        <v>172</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2200000</v>
+        <v>750000</v>
       </c>
       <c r="AA8" t="n">
-        <v>149</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1247,91 +1278,83 @@
       <c r="K9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>21.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
-        <v>174</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="S9" t="n">
-        <v>15450000</v>
+        <v>6050000</v>
       </c>
       <c r="T9" t="n">
-        <v>229</v>
+        <v>411</v>
       </c>
       <c r="U9" t="n">
-        <v>22.33333333333333</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="W9" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="Z9" t="n">
-        <v>19600000</v>
+        <v>375000</v>
       </c>
       <c r="AA9" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
+          <t xml:space="preserve">dujic f 
   can </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>22423</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1348,89 +1371,71 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>175</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>875000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>72</v>
-      </c>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>28</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>725000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>66</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  mo </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18500</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1447,19 +1452,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>181.5</v>
+        <v>179</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1468,68 +1473,68 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="S11" t="n">
-        <v>2000000</v>
+        <v>2240000</v>
       </c>
       <c r="T11" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>180.6666666666667</v>
+        <v>182.5</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="AA11" t="n">
-        <v>207</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22423</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1546,75 +1551,85 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>27</v>
+      </c>
+      <c r="O12" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>265</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="T12" t="n">
+        <v>281</v>
+      </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2240000</v>
+        <v>2900000</v>
       </c>
       <c r="AA12" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1632,31 +1647,31 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O13" t="n">
-        <v>175</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="S13" t="n">
-        <v>2900000</v>
+        <v>5000000</v>
       </c>
       <c r="T13" t="n">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -1665,10 +1680,10 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="n">
-        <v>1350000</v>
+        <v>2400000</v>
       </c>
       <c r="AA13" t="n">
         <v>145</v>
@@ -1677,35 +1692,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18000</v>
+        <v>25218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1720,38 +1735,42 @@
       <c r="K14" t="n">
         <v>2024</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O14" t="n">
-        <v>181.5</v>
+        <v>178</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="S14" t="n">
-        <v>2500000</v>
+        <v>775000</v>
       </c>
       <c r="T14" t="n">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V14" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
@@ -1760,13 +1779,98 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Z14" t="n">
-        <v>775000</v>
+        <v>1300000</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>167</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>174</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>206</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="O7" t="n">
-        <v>179</v>
+        <v>181.4</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1103,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="S7" t="n">
-        <v>15575000</v>
+        <v>12875000</v>
       </c>
       <c r="T7" t="n">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1383,25 +1383,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>25.25</v>
+        <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>177</v>
+        <v>175.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="Z10" t="n">
-        <v>8600000</v>
+        <v>56100000</v>
       </c>
       <c r="AA10" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="V13" t="n">
-        <v>183</v>
+        <v>181.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -1680,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="Z13" t="n">
-        <v>2400000</v>
+        <v>1300000</v>
       </c>
       <c r="AA13" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -1668,25 +1668,25 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="V13" t="n">
-        <v>181.5</v>
+        <v>188</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="Z13" t="n">
-        <v>1300000</v>
+        <v>800000</v>
       </c>
       <c r="AA13" t="n">
-        <v>135</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -1091,10 +1091,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>29.2</v>
+        <v>28.8</v>
       </c>
       <c r="O7" t="n">
-        <v>181.4</v>
+        <v>179</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1103,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="S7" t="n">
-        <v>12875000</v>
+        <v>15575000</v>
       </c>
       <c r="T7" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -1383,25 +1383,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>24.6</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>175.8</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>56100000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>380</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
@@ -1668,25 +1668,25 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V13" t="n">
-        <v>188</v>
+        <v>185.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="Z13" t="n">
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="AA13" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -901,25 +901,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19.33333333333333</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="S5" t="n">
-        <v>1600000</v>
+        <v>7600000</v>
       </c>
       <c r="T5" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="U5" t="n">
         <v>29.2</v>
@@ -996,46 +996,46 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>186.5</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="S6" t="n">
-        <v>615000</v>
+        <v>2815000</v>
       </c>
       <c r="T6" t="n">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="U6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V6" t="n">
-        <v>183.6666666666667</v>
+        <v>180</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="Z6" t="n">
-        <v>3275000</v>
+        <v>6775000</v>
       </c>
       <c r="AA6" t="n">
-        <v>204</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
@@ -1091,10 +1091,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="O7" t="n">
-        <v>179</v>
+        <v>181.4</v>
       </c>
       <c r="P7" t="n">
         <v>1.4</v>
@@ -1103,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="S7" t="n">
-        <v>15575000</v>
+        <v>12875000</v>
       </c>
       <c r="T7" t="n">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="U7" t="n">
         <v>34</v>
@@ -1383,25 +1383,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>25.25</v>
+        <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>177</v>
+        <v>175.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="Z10" t="n">
-        <v>8600000</v>
+        <v>56100000</v>
       </c>
       <c r="AA10" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11">
@@ -1668,10 +1668,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>185.5</v>
+        <v>183</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -1680,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="n">
-        <v>1200000</v>
+        <v>2400000</v>
       </c>
       <c r="AA13" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,25 +1383,25 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>24.6</v>
+        <v>25.25</v>
       </c>
       <c r="V10" t="n">
-        <v>175.8</v>
+        <v>177</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="Z10" t="n">
-        <v>56100000</v>
+        <v>8600000</v>
       </c>
       <c r="AA10" t="n">
-        <v>380</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
@@ -1668,10 +1668,10 @@
         <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="V13" t="n">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -1680,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="Z13" t="n">
-        <v>2400000</v>
+        <v>1225000</v>
       </c>
       <c r="AA13" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -1873,6 +1873,1704 @@
         <v>229</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>167</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>167</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>167</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>167</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>167</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>167</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>167</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>167</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,30 +465,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
@@ -501,7 +511,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -528,24 +538,34 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
@@ -558,7 +578,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,20 +605,30 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
@@ -611,9 +641,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -633,24 +668,34 @@
           <t>tr3oe8I8</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -659,7 +704,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -686,20 +731,30 @@
           <t>zsdfgnmL</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>167</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1671</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>j9cigLCr</t>
         </is>
@@ -712,7 +767,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -739,24 +794,34 @@
           <t>UwAwNo2E</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>167</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1671</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>tr3oe8I8</t>
         </is>
@@ -769,7 +834,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -796,24 +861,34 @@
           <t>QJF7WTFB</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>167</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1671</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2024</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
@@ -826,7 +901,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -853,24 +928,26 @@
           <t>IeT6JBE3</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>167</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1671</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>2024</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
@@ -883,7 +960,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -910,24 +987,26 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>167</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1671</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -936,7 +1015,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -963,297 +1042,26 @@
           <t>EPngUvhk</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
         <v>167</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1671</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2024</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18061</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>167</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>167</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>167</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>167</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>167</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,40 +465,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>season</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home_rival_team</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
@@ -507,561 +497,165 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20371</v>
+        <v>22000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>167</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1671</v>
       </c>
       <c r="J2" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>25218</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>167</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1671</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>72000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>167</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1671</v>
       </c>
       <c r="J4" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>zV5YmQAr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>167</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Uw6sTk0t</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>167</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>167</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>19400</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>167</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>167</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22423</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>167</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,30 +465,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
@@ -528,20 +538,30 @@
           <t>x05z14ue</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -577,24 +597,34 @@
           <t>K2dlua5N</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
@@ -634,24 +664,34 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,40 +465,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>season</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home_rival_team</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
@@ -507,193 +497,2040 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>167</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>167</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>167</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>167</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>167</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>167</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>167</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>167</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>167</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo stadium
   los angeles  ca </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>22000</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>167</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>167</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">providence park
   portland  or </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E12" t="n">
         <v>25218</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>167</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
   seattle  wa </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E14" t="n">
         <v>72000</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>167</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>167</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>167</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>167</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>167</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N4" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="H26" t="n">
+        <v>167</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>167</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>167</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45480.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45480.0625</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>167</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45480.10416666666</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45481.0625</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>167</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45481.83333333334</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,10 +485,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
@@ -497,35 +507,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20371</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -542,47 +547,48 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>71000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -597,40 +603,50 @@
       <c r="K3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -647,96 +663,110 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>167</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
   harrison  nj </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>25000</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>zV5YmQAr</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>167</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -753,47 +783,44 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18500</v>
+        <v>20500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -810,47 +837,52 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19400</v>
+        <v>22039</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -867,30 +899,35 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">geodis park
@@ -907,7 +944,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -924,43 +961,52 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22423</v>
+        <v>18500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -977,43 +1023,52 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>22000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1030,47 +1085,48 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>25218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1087,43 +1143,52 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1138,41 +1203,46 @@
       <c r="K13" t="n">
         <v>2024</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1189,47 +1259,52 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72000</v>
+        <v>54405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1246,12 +1321,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -561,6 +631,48 @@
           <t>nezMCpx2</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>185</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U2" t="n">
+        <v>375000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>317</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4765000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -619,6 +731,20 @@
           <t>j9cigLCr</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -681,6 +807,20 @@
           <t>vZraQYnO</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -739,6 +879,20 @@
           <t>8btog05R</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -793,6 +947,20 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -855,6 +1023,20 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -917,6 +1099,20 @@
           <t>nezMCpx2</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -979,6 +1175,20 @@
           <t>rsHkUNCo</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1041,6 +1251,20 @@
           <t>2i4sdl32</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1099,6 +1323,20 @@
           <t>W0ealpQl</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1161,6 +1399,20 @@
           <t>CURGfJWt</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1215,6 +1467,20 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1277,6 +1543,20 @@
           <t>tr3oe8I8</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1339,6 +1619,2296 @@
           <t>CURGfJWt</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>167</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>167</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>167</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>167</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>167</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>167</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>167</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>167</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45479.89583333334</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>167</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>167</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>167</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>167</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>167</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>167</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>167</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>167</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -583,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45471.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">yankee stadium
@@ -683,7 +688,12 @@
       <c r="B3" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -731,20 +741,48 @@
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>177</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>279</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>292</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>524</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7565000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>542</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -755,7 +793,12 @@
       <c r="B4" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -807,20 +850,48 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>120</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>128</v>
+      </c>
+      <c r="W4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>353</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15575000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -831,7 +902,12 @@
       <c r="B5" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -879,20 +955,48 @@
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>172.3333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>206</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>214</v>
+      </c>
+      <c r="W5" t="n">
+        <v>37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -903,7 +1007,12 @@
       <c r="B6" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -947,20 +1056,48 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>310</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>362</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>187.1666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>383</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>426</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -971,7 +1108,12 @@
       <c r="B7" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">toyota stadium
@@ -1023,20 +1165,48 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>206</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>229</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>284</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>295</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1047,7 +1217,12 @@
       <c r="B8" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -1099,13 +1274,27 @@
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>875000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>72</v>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -1123,7 +1312,12 @@
       <c r="B9" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">geodis park
@@ -1175,20 +1369,48 @@
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>392</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>411</v>
+      </c>
+      <c r="W9" t="n">
+        <v>28.42857142857143</v>
+      </c>
+      <c r="X9" t="n">
+        <v>178.2857142857143</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>535</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>84725000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>557</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1199,7 +1421,12 @@
       <c r="B10" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1251,13 +1478,27 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>129</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>137</v>
+      </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1275,7 +1516,12 @@
       <c r="B11" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo stadium
@@ -1323,20 +1569,48 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>68</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20</v>
+      </c>
+      <c r="X11" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>118</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1347,7 +1621,12 @@
       <c r="B12" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">providence park
@@ -1399,20 +1678,48 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>179</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>130</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>130</v>
+      </c>
+      <c r="W12" t="n">
+        <v>23</v>
+      </c>
+      <c r="X12" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1423,7 +1730,12 @@
       <c r="B13" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">paypal park
@@ -1467,20 +1779,48 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>197</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>206</v>
+      </c>
+      <c r="W13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>172</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1491,7 +1831,12 @@
       <c r="B14" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1550,13 +1895,27 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6775000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>278</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1567,7 +1926,12 @@
       <c r="B15" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -1619,13 +1983,27 @@
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>137</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>137</v>
+      </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -577,35 +577,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23112</v>
+        <v>71000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,24 +625,38 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>135</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>146</v>
+      </c>
       <c r="W2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="X2" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -656,47 +665,42 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2300000</v>
+        <v>50000</v>
       </c>
       <c r="AC2" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -721,87 +725,86 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q3" t="n">
-        <v>185.5</v>
+        <v>191</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>260</v>
+        <v>58</v>
       </c>
       <c r="U3" t="n">
-        <v>3750000</v>
+        <v>140000</v>
       </c>
       <c r="V3" t="n">
-        <v>282</v>
+        <v>58</v>
       </c>
       <c r="W3" t="n">
-        <v>26.6</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>179.6</v>
+        <v>181.5</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>318</v>
+        <v>117</v>
       </c>
       <c r="AB3" t="n">
-        <v>3225000</v>
+        <v>990000</v>
       </c>
       <c r="AC3" t="n">
-        <v>331</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>21550</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -828,72 +831,67 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25.33333333333333</v>
+        <v>27.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>181.3333333333333</v>
+        <v>177.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="U4" t="n">
-        <v>4530000</v>
+        <v>56625000</v>
       </c>
       <c r="V4" t="n">
-        <v>203</v>
+        <v>313</v>
       </c>
       <c r="W4" t="n">
-        <v>28</v>
+        <v>25.8</v>
       </c>
       <c r="X4" t="n">
-        <v>186.5</v>
+        <v>177.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="AB4" t="n">
-        <v>900000</v>
+        <v>8875000</v>
       </c>
       <c r="AC4" t="n">
-        <v>135</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -910,7 +908,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -938,7 +936,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -963,59 +961,54 @@
         <v>146</v>
       </c>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>185</v>
+        <v>176.6666666666667</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>58</v>
+        <v>420</v>
       </c>
       <c r="AB5" t="n">
-        <v>475000</v>
+        <v>35150000</v>
       </c>
       <c r="AC5" t="n">
-        <v>72</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30991</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1040,91 +1033,82 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.6666666666667</v>
+        <v>183.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="U6" t="n">
-        <v>11490000</v>
+        <v>3300000</v>
       </c>
       <c r="V6" t="n">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="X6" t="n">
-        <v>183.6666666666667</v>
+        <v>182.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>206</v>
+        <v>321</v>
       </c>
       <c r="AB6" t="n">
-        <v>8375000</v>
+        <v>3855000</v>
       </c>
       <c r="AC6" t="n">
-        <v>213</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20700</v>
+        <v>25500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1151,61 +1135,80 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>185</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>475000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>72</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>242</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3395000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>274</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61500</v>
+        <v>18500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1232,71 +1235,84 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>27.2</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>337</v>
+        <v>56</v>
       </c>
       <c r="U8" t="n">
-        <v>5575000</v>
+        <v>275000</v>
       </c>
       <c r="V8" t="n">
-        <v>351</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="W8" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>255</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>268</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">touchan r 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20500</v>
+        <v>20738</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1326,82 +1342,81 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>22.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>27050000</v>
+        <v>15000000</v>
       </c>
       <c r="V9" t="n">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="W9" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="X9" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AB9" t="n">
-        <v>2900000</v>
+        <v>1150000</v>
       </c>
       <c r="AC9" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>19400</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1428,89 +1443,80 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
           <t>CURGfJWt</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>29.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>175</v>
+        <v>186.25</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>253</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>260</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
-        <v>130</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1975000</v>
-      </c>
-      <c r="V10" t="n">
-        <v>140</v>
-      </c>
-      <c r="W10" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="X10" t="n">
-        <v>185.6666666666667</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
       <c r="AA10" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="AB10" t="n">
-        <v>1270000</v>
+        <v>1225000</v>
       </c>
       <c r="AC10" t="n">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>21650</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1537,58 +1543,53 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
-        <v>27</v>
-      </c>
-      <c r="X11" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="T11" t="n">
+        <v>129</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V11" t="n">
         <v>137</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>139</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45486.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.9375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1605,7 +1606,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1635,7 +1636,11 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
       <c r="P12" t="n">
         <v>22</v>
       </c>
@@ -1658,59 +1663,54 @@
         <v>77</v>
       </c>
       <c r="W12" t="n">
-        <v>19.33333333333333</v>
+        <v>26.4</v>
       </c>
       <c r="X12" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="AB12" t="n">
-        <v>1600000</v>
+        <v>10375000</v>
       </c>
       <c r="AC12" t="n">
-        <v>210</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45486.97569444445</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1737,89 +1737,66 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>178</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>775000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>65</v>
-      </c>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="X13" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y13" t="n">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="AB13" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="AC13" t="n">
-        <v>131</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45486.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22000</v>
+        <v>54405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1844,38 +1821,42 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>21.5</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="U14" t="n">
-        <v>3200000</v>
+        <v>1300000</v>
       </c>
       <c r="V14" t="n">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="W14" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="X14" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -1884,47 +1865,42 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB14" t="n">
-        <v>50000</v>
+        <v>875000</v>
       </c>
       <c r="AC14" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45486.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.98958333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1952,14 +1928,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="n">
-        <v>185.5</v>
+        <v>175</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1968,34 +1944,34 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="U15" t="n">
-        <v>1225000</v>
+        <v>5100000</v>
       </c>
       <c r="V15" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="W15" t="n">
-        <v>24.66666666666667</v>
+        <v>31.5</v>
       </c>
       <c r="X15" t="n">
-        <v>180.3333333333333</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="AB15" t="n">
-        <v>2500000</v>
+        <v>1375000</v>
       </c>
       <c r="AC15" t="n">
-        <v>202</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:BC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,110 +465,240 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_val_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_val_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
@@ -583,7 +713,12 @@
       <c r="B2" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -603,74 +738,142 @@
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>174.5</v>
-      </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="T2" t="n">
-        <v>135</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="U2" t="n">
-        <v>3800000</v>
+        <v>66.72727272727273</v>
       </c>
       <c r="V2" t="n">
-        <v>146</v>
+        <v>1174090.909090909</v>
       </c>
       <c r="W2" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3570000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>27.16666666666667</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>179</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1262500</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>179</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1532142.857142857</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
         <v>37</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AX2" t="n">
         <v>186</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
         <v>63</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="BB2" t="n">
         <v>50000</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="BC2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -683,7 +886,12 @@
       <c r="B3" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -703,78 +911,160 @@
           <t>zsdfgnmL</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>zsdfgnmL</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>191</v>
-      </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>179.1818181818182</v>
       </c>
       <c r="T3" t="n">
-        <v>58</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="U3" t="n">
-        <v>140000</v>
+        <v>66.36363636363636</v>
       </c>
       <c r="V3" t="n">
-        <v>58</v>
+        <v>1318181.818181818</v>
       </c>
       <c r="W3" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="X3" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3235909.090909091</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1582222.222222222</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>184</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>678750</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>187</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>124</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>127</v>
+      </c>
+      <c r="AW3" t="n">
         <v>23</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AX3" t="n">
         <v>181.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="BA3" t="n">
         <v>117</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="BB3" t="n">
         <v>990000</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="BC3" t="n">
         <v>129</v>
       </c>
     </row>
@@ -787,7 +1077,12 @@
       <c r="B4" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -807,78 +1102,160 @@
           <t>UwAwNo2E</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>tr3oe8I8</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>177.75</v>
-      </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>26.90909090909091</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>183.2727272727273</v>
       </c>
       <c r="T4" t="n">
-        <v>301</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="U4" t="n">
-        <v>56625000</v>
+        <v>73.81818181818181</v>
       </c>
       <c r="V4" t="n">
-        <v>313</v>
+        <v>6020454.545454546</v>
       </c>
       <c r="W4" t="n">
+        <v>77.18181818181819</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2327272.727272727</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>62.85714285714285</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>917857.1428571428</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>61.44444444444444</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>713888.8888888889</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>372</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>57825000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>384</v>
+      </c>
+      <c r="AW4" t="n">
         <v>25.8</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AX4" t="n">
         <v>177.4</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AY4" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AZ4" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="BA4" t="n">
         <v>337</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="BB4" t="n">
         <v>8875000</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="BC4" t="n">
         <v>358</v>
       </c>
     </row>
@@ -891,7 +1268,12 @@
       <c r="B5" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -911,75 +1293,157 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>167</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1671</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>173.5</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="T5" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>8800000</v>
+        <v>67.44444444444444</v>
       </c>
       <c r="V5" t="n">
-        <v>146</v>
+        <v>1222222.222222222</v>
       </c>
       <c r="W5" t="n">
-        <v>21.66666666666667</v>
+        <v>70</v>
       </c>
       <c r="X5" t="n">
-        <v>176.6666666666667</v>
+        <v>25.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>181.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>420</v>
+        <v>64.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>35150000</v>
+        <v>1017500</v>
       </c>
       <c r="AC5" t="n">
-        <v>467</v>
+        <v>68.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>178.4285714285714</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>63.57142857142857</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>642857.1428571428</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>69.85714285714286</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>294285.7142857143</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>66.28571428571429</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>177.7142857142857</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>493</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>34100000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>530</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>178</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>561</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>42350000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>611</v>
       </c>
     </row>
     <row r="6">
@@ -991,7 +1455,12 @@
       <c r="B6" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -1011,75 +1480,157 @@
           <t>8btog05R</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>167</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1671</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>pQ8rarA7</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>183.5</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>21.8</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>180.5</v>
       </c>
       <c r="T6" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3300000</v>
+        <v>64.5</v>
       </c>
       <c r="V6" t="n">
-        <v>282</v>
+        <v>1732000</v>
       </c>
       <c r="W6" t="n">
-        <v>27.8</v>
+        <v>72.7</v>
       </c>
       <c r="X6" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1640454.545454545</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23.42857142857143</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>181.2857142857143</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>60.28571428571428</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>948571.4285714285</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>69.42857142857143</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>178.4444444444445</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>63.66666666666666</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3575000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>182.2</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AR6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS6" t="n">
         <v>5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>321</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3855000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>330</v>
+      <c r="AT6" t="n">
+        <v>319</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>17800000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>361</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>199</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="7">
@@ -1091,7 +1642,12 @@
       <c r="B7" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">inter co stadium
@@ -1111,75 +1667,157 @@
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>167</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1671</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2024</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2192500</v>
+      </c>
+      <c r="W7" t="n">
+        <v>72</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22.55555555555556</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>65.88888888888889</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1555555.555555556</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>183</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>63.625</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2819375</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21.57142857142857</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>183</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>62.71428571428572</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1846428.571428571</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP7" t="n">
         <v>20</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AQ7" t="n">
         <v>185</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
         <v>58</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AU7" t="n">
         <v>475000</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AV7" t="n">
         <v>72</v>
       </c>
-      <c r="W7" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>242</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3395000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>274</v>
+      <c r="AW7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>118</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -1191,7 +1829,12 @@
       <c r="B8" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">subaru park
@@ -1211,79 +1854,161 @@
           <t>84yIDQMe</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>167</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1671</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>2024</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="S8" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="U8" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3277272.727272727</v>
+      </c>
+      <c r="W8" t="n">
+        <v>73.72727272727273</v>
+      </c>
+      <c r="X8" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>182.9090909090909</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65.72727272727273</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2627727.272727273</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>961666.6666666666</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>65.83333333333333</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AP8" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AQ8" t="n">
         <v>175</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
         <v>56</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AU8" t="n">
         <v>275000</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AV8" t="n">
         <v>63</v>
       </c>
-      <c r="W8" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>255</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>268</v>
+      <c r="AW8" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>185</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -1295,7 +2020,12 @@
       <c r="B9" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">q2 stadium
@@ -1315,78 +2045,104 @@
           <t>QJF7WTFB</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>167</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1671</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
         <v>27</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AQ9" t="n">
         <v>179</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AR9" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
         <v>78</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AU9" t="n">
         <v>15000000</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AV9" t="n">
         <v>78</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AW9" t="n">
         <v>32.5</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AX9" t="n">
         <v>180</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>2</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="BA9" t="n">
         <v>135</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="BB9" t="n">
         <v>1150000</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="BC9" t="n">
         <v>135</v>
       </c>
     </row>
@@ -1399,7 +2155,12 @@
       <c r="B10" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">allianz field
@@ -1419,74 +2180,100 @@
           <t>x05z14ue</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
         <v>167</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1671</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2024</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AQ10" t="n">
         <v>186.25</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AT10" t="n">
         <v>253</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AU10" t="n">
         <v>1720000</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AV10" t="n">
         <v>260</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AW10" t="n">
         <v>24.5</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AX10" t="n">
         <v>185.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>2</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="BA10" t="n">
         <v>125</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="BB10" t="n">
         <v>1225000</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="BC10" t="n">
         <v>134</v>
       </c>
     </row>
@@ -1499,7 +2286,12 @@
       <c r="B11" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1519,59 +2311,45 @@
           <t>4r4sKQud</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
         <v>167</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>1671</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2024</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>129</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>137</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
@@ -1579,6 +2357,46 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>129</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>137</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1589,7 +2407,12 @@
       <c r="B12" s="2" t="n">
         <v>45493.9375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1609,78 +2432,104 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>167</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1671</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>2024</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>jmBZNRn8</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
         <v>22</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AQ12" t="n">
         <v>183</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
         <v>67</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AU12" t="n">
         <v>2100000</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AV12" t="n">
         <v>77</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AW12" t="n">
         <v>26.4</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AX12" t="n">
         <v>179</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>5</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="BA12" t="n">
         <v>333</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="BB12" t="n">
         <v>10375000</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="BC12" t="n">
         <v>355</v>
       </c>
     </row>
@@ -1693,7 +2542,12 @@
       <c r="B13" s="2" t="n">
         <v>45493.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1713,60 +2567,86 @@
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>167</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1671</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>2024</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="n">
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
         <v>19</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AX13" t="n">
         <v>189</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AY13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="n">
         <v>58</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="BB13" t="n">
         <v>400000</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="BC13" t="n">
         <v>68</v>
       </c>
     </row>
@@ -1779,7 +2659,12 @@
       <c r="B14" s="2" t="n">
         <v>45493.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -1799,78 +2684,104 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
         <v>167</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1671</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>2024</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
         <v>26</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AQ14" t="n">
         <v>185</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
         <v>68</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AU14" t="n">
         <v>1300000</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AV14" t="n">
         <v>70</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AW14" t="n">
         <v>20</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AX14" t="n">
         <v>175</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="n">
         <v>62</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="BB14" t="n">
         <v>875000</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="BC14" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1883,7 +2794,12 @@
       <c r="B15" s="2" t="n">
         <v>45493.98958333334</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">dignity health sports park
@@ -1903,74 +2819,100 @@
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
         <v>167</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>1671</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>2024</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
         <v>26</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="AQ15" t="n">
         <v>175</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AT15" t="n">
         <v>140</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AU15" t="n">
         <v>5100000</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AV15" t="n">
         <v>148</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AW15" t="n">
         <v>31.5</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AX15" t="n">
         <v>175</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AY15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="BA15" t="n">
         <v>138</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="BB15" t="n">
         <v>1375000</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="BC15" t="n">
         <v>138</v>
       </c>
     </row>
